--- a/data/trans_orig/IP19C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15359</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30219</t>
+          <t>30003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>39826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37396</t>
+          <t>37535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>61631</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74457</t>
+          <t>74556</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44363</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65344</t>
+          <t>64475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33173</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51985</t>
+          <t>50857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82571</t>
+          <t>82825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>109755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162978</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183959</t>
+          <t>184293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>193738</t>
+          <t>194866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>213397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>362044</t>
+          <t>364290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391474</t>
+          <t>391220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>17714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63452</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71683</t>
+          <t>71933</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>65566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>122320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135615</t>
+          <t>135567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>75264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>265072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289214</t>
+          <t>288475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309536</t>
+          <t>308853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>560594</t>
+          <t>559842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>591775</t>
+          <t>593028</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34832</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39991</t>
+          <t>39940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>23070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33255</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>56200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39279</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58022</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>39706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84551</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113335</t>
+          <t>113070</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162456</t>
+          <t>161186</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181199</t>
+          <t>181050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180863</t>
+          <t>180435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201550</t>
+          <t>201207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348056</t>
+          <t>348321</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376840</t>
+          <t>376183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78018</t>
+          <t>77982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71183</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79092</t>
+          <t>79234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>140821</t>
+          <t>141648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154704</t>
+          <t>154927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>60546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85384</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>161024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>268504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>292807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283100</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>308353</t>
+          <t>306710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>557050</t>
+          <t>558903</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593098</t>
+          <t>594132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>45,42%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>12949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>21797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38192</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59721</t>
+          <t>58583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36862</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57449</t>
+          <t>57092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81088</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108838</t>
+          <t>111389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193019</t>
+          <t>194157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214160</t>
+          <t>214548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195471</t>
+          <t>195828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>216058</t>
+          <t>216830</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>396821</t>
+          <t>394270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>424571</t>
+          <t>424088</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11649</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76091</t>
+          <t>75744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71475</t>
+          <t>71734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81442</t>
+          <t>81274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151462</t>
+          <t>151311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>164703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>73260</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288675</t>
+          <t>289358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>289600</t>
+          <t>287711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>313919</t>
+          <t>312918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>583581</t>
+          <t>586020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>617418</t>
+          <t>618799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27215</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34790</t>
+          <t>34955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36255</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57290</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45884</t>
+          <t>45170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73834</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89214</t>
+          <t>88421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122792</t>
+          <t>123167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>204537</t>
+          <t>204652</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>225572</t>
+          <t>226008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249181</t>
+          <t>249134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277131</t>
+          <t>277845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>462050</t>
+          <t>461675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>495628</t>
+          <t>496421</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>25530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22929</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77912</t>
+          <t>77996</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89598</t>
+          <t>89544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>110415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126014</t>
+          <t>125965</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193934</t>
+          <t>194121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213092</t>
+          <t>213138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96364</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>129528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169935</t>
+          <t>169743</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>307607</t>
+          <t>308711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335203</t>
+          <t>336696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>388080</t>
+          <t>389510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>419114</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>706333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749908</t>
+          <t>746548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C03-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9430</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5640</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>33,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11593</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7100</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9430</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5356</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14055</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,99%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>28176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28688</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37251</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>66,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35333</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30003</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39826</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30188</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39633</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>63,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33461</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>28836</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37535</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,01%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74556</t>
+          <t>74370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42891</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>46926</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42891</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41781</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33256</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>51383</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>53953</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44029</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>64475</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>44639</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>64446</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>41781</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>32326</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>50857</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82825</t>
+          <t>81130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109755</t>
+          <t>109198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>203942</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>194340</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212467</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>174369</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>163847</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184293</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>163876</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>183683</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>203942</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>194866</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>213397</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>364290</t>
+          <t>364847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>391220</t>
+          <t>392915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>245723</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>343</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>228322</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>245723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12260</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18051</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7243</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12064</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12679</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12260</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7551</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17714</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,77%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13237</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60857</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>55066</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65473</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68440</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63619</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>71933</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>63004</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>71812</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60857</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55403</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65566</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,23%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122320</t>
+          <t>122293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135567</t>
+          <t>135563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -1640,52 +1640,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>73117</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75683</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>73117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>74619</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62455</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85858</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60600</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85800</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52878</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>75264</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119633</t>
+          <t>119807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>152819</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>298260</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>287112</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>309100</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>278141</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>265072</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>288475</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>265130</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>290330</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>298260</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>286467</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>308853</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559842</t>
+          <t>557196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593028</t>
+          <t>592854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15014</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9725</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11734</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7387</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16774</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7458</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17427</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>24,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15014</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9745</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28521</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23054</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>33810</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35593</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30553</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39940</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>29900</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39869</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>75,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28521</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23070</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>33790</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56200</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70845</t>
+          <t>71132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,29%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43535</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43535</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43535</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47327</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43535</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>43535</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40789</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>61343</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48627</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39428</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>59292</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>39402</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59205</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>22,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>49828</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>39706</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>60478</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113070</t>
+          <t>113919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>191085</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>179570</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>200124</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>79,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>171851</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>161186</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181050</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>161273</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>181076</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>77,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>191085</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>180435</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>201207</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>79,32%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348321</t>
+          <t>347472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376183</t>
+          <t>375780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>240913</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>220478</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>240913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6277</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3245</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11092</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12583</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7566</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19154</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7952</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19057</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6277</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11382</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12746</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>26287</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75848</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78880</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>72965</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66394</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77982</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77596</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>85,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75848</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70743</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79234</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141648</t>
+          <t>141386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>154891</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82125</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>85548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58627</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83973</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>60546</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>84849</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62117</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85259</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>59864</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>83812</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125795</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161024</t>
+          <t>160607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>295454</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>282601</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>307947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>396</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>280409</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>268504</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>292807</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>268094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>291236</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>79,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>295454</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>282762</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>306710</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558903</t>
+          <t>559320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>594132</t>
+          <t>592232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>353353</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6214</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14497</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6269</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3372</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10161</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10478</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>28,32%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10399</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6344</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15192</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17742</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13644</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21927</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15870</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11978</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18767</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11661</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18934</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>71,68%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17742</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12949</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21797</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28141</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22139</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46491</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36340</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>57282</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>48382</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>38192</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>58583</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38252</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59163</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>46491</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36090</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57092</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81571</t>
+          <t>80951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111389</t>
+          <t>109922</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>206429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>195638</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>216580</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204358</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>194157</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>214548</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>193577</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>214488</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>206429</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>195828</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>216830</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>394270</t>
+          <t>395737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>424088</t>
+          <t>424708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>252920</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>252920</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>252920</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>370</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252740</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>252920</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>252920</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>252920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15957</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6980</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11996</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3734</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12304</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>10201</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6424</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15964</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>24943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>77497</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>71741</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81908</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>80760</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>75744</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84144</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75436</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84006</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,04%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>77497</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71734</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>81274</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,37%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151311</t>
+          <t>150494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164703</t>
+          <t>164173</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87698</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>87740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>87698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4963,67 +4963,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>56471</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80516</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>51337</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>73260</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>49923</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73348</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>55840</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>81047</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>112503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145356</t>
+          <t>146019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>301668</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>288242</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>312287</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>84,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>300987</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>289358</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>311281</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>289270</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>312695</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>301668</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>287711</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>312918</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>586020</t>
+          <t>585357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>618799</t>
+          <t>618873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8638</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7165</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14937</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20374</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15652</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>64,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22565</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14793</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26992</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>75,9%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>42543</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>46671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24290</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29730</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>54979</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43801</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70058</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>46329</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>35819</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>57175</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58420</t>
+          <t>47378</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45170</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73881</t>
+          <t>58620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>104749</t>
+          <t>102356</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88421</t>
+          <t>85546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>119452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254566</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>239487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>265744</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>215498</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>204652</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>226008</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>82,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>218674</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249134</t>
+          <t>207432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277845</t>
+          <t>228053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>480093</t>
+          <t>473241</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>461675</t>
+          <t>456145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>496421</t>
+          <t>490051</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>309545</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>261827</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>323015</t>
+          <t>266052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>584842</t>
+          <t>575597</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13976</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8267</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21390</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15412</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10532</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22080</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16483</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>29436</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>113284</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>105870</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>118993</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,19%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>84664</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77996</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89544</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>119462</t>
+          <t>88122</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>81281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125965</t>
+          <t>93961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>204126</t>
+          <t>201406</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194121</t>
+          <t>191217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213138</t>
+          <t>209388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127260</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100076</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135945</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>236021</t>
+          <t>230842</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>58072</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88226</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>54937</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82922</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>122944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169743</t>
+          <t>160070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>388225</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>372869</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>403023</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>322727</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>308711</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>336696</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>405656</t>
+          <t>328966</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>389510</t>
+          <t>316567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421128</t>
+          <t>340633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>728382</t>
+          <t>717190</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706333</t>
+          <t>697302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>746548</t>
+          <t>734428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
